--- a/dataset_t6_grouped/results2/G4/G4_T4883_W0074F0001T0006Z000C1N24_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T4883_W0074F0001T0006Z000C1N24_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>34.50789269387146</v>
+        <v>5.607532562754113</v>
       </c>
       <c r="D2" t="n">
-        <v>34.7347600207682</v>
+        <v>5.644398503374832</v>
       </c>
       <c r="E2" t="n">
-        <v>12.45357560543483</v>
+        <v>2.02370603588316</v>
       </c>
       <c r="F2" t="n">
-        <v>7.028894156726198</v>
+        <v>1.142195300468007</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>36.4265314634351</v>
+        <v>5.919311362808203</v>
       </c>
       <c r="D3" t="n">
-        <v>35.93243989298885</v>
+        <v>5.839021482610688</v>
       </c>
       <c r="E3" t="n">
-        <v>12.45357560543483</v>
+        <v>2.02370603588316</v>
       </c>
       <c r="F3" t="n">
-        <v>7.028894156726198</v>
+        <v>1.142195300468007</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>15.90876847725796</v>
+        <v>2.585174877554419</v>
       </c>
       <c r="D4" t="n">
-        <v>15.90120975230784</v>
+        <v>2.583946584750025</v>
       </c>
       <c r="E4" t="n">
-        <v>12.45357560543483</v>
+        <v>2.02370603588316</v>
       </c>
       <c r="F4" t="n">
-        <v>7.028894156726198</v>
+        <v>1.142195300468007</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>42.04890710461753</v>
+        <v>6.83294740450035</v>
       </c>
       <c r="D5" t="n">
-        <v>35.62917111893355</v>
+        <v>5.789740306826702</v>
       </c>
       <c r="E5" t="n">
-        <v>12.45357560543483</v>
+        <v>2.02370603588316</v>
       </c>
       <c r="F5" t="n">
-        <v>7.028894156726198</v>
+        <v>1.142195300468007</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>45.91043007945282</v>
+        <v>7.460444887911083</v>
       </c>
       <c r="D6" t="n">
-        <v>37.1114748598448</v>
+        <v>6.030614664724781</v>
       </c>
       <c r="E6" t="n">
-        <v>12.45357560543483</v>
+        <v>2.02370603588316</v>
       </c>
       <c r="F6" t="n">
-        <v>7.028894156726198</v>
+        <v>1.142195300468007</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>9.429604848721736</v>
+        <v>1.532310787917282</v>
       </c>
       <c r="D7" t="n">
-        <v>26.501166039373</v>
+        <v>4.306439481398113</v>
       </c>
       <c r="E7" t="n">
-        <v>12.45357560543483</v>
+        <v>2.02370603588316</v>
       </c>
       <c r="F7" t="n">
-        <v>7.028894156726198</v>
+        <v>1.142195300468007</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>33.55955307176929</v>
+        <v>5.45342737416251</v>
       </c>
       <c r="D8" t="n">
-        <v>30.1502138565858</v>
+        <v>4.899409751695193</v>
       </c>
       <c r="E8" t="n">
-        <v>12.45357560543483</v>
+        <v>2.02370603588316</v>
       </c>
       <c r="F8" t="n">
-        <v>7.028894156726198</v>
+        <v>1.142195300468007</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
